--- a/xls/square_20_tri3_11.xlsx
+++ b/xls/square_20_tri3_11.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>441</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>486</v>
+      </c>
+      <c r="I9">
+        <v>7.309054242515279</v>
+      </c>
+      <c r="J9">
+        <v>3.10994809655159</v>
+      </c>
+      <c r="K9">
+        <v>3.017469640524186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>144</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>441</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>600</v>
+      </c>
+      <c r="I10">
+        <v>4.683234445429636</v>
+      </c>
+      <c r="J10">
+        <v>0.9013277748998003</v>
+      </c>
+      <c r="K10">
+        <v>1.701765321874042</v>
+      </c>
+    </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
